--- a/Data/FlightPlan/FPL_23AUG26.xlsx
+++ b/Data/FlightPlan/FPL_23AUG26.xlsx
@@ -428,7 +428,7 @@
     <t>13:00</t>
   </si>
   <si>
-    <t>12:53</t>
+    <t>13:08</t>
   </si>
   <si>
     <t>DLI</t>
@@ -551,6 +551,9 @@
     <t>13:15</t>
   </si>
   <si>
+    <t>13:29</t>
+  </si>
+  <si>
     <t>16:10</t>
   </si>
   <si>
@@ -635,6 +638,9 @@
     <t>11:12</t>
   </si>
   <si>
+    <t>13:22</t>
+  </si>
+  <si>
     <t>18:45</t>
   </si>
   <si>
@@ -674,753 +680,798 @@
     <t>11:25</t>
   </si>
   <si>
+    <t>13:19</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>13:46</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>14:46</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>08:38</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>13:27</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>15:57</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>11:58</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>07:34</t>
+  </si>
+  <si>
+    <t>09:29</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>16:06</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>08:09</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>10:56</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>13:24</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>10:21</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>10:34</t>
+  </si>
+  <si>
+    <t>12:54</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:03</t>
+  </si>
+  <si>
+    <t>14:13</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>07:59</t>
+  </si>
+  <si>
+    <t>14:08</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>10:44</t>
+  </si>
+  <si>
+    <t>12:58</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>09:43</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>12:37</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>13:57</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>12:09</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>07:23</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>13:14</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>10:47</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>886D</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:03</t>
+  </si>
+  <si>
+    <t>10:43</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>12:07</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>09:57</t>
+  </si>
+  <si>
+    <t>12:26</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>06:56</t>
+  </si>
+  <si>
+    <t>09:18</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>12:52</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>14:06</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>07:31</t>
+  </si>
+  <si>
+    <t>09:02</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>09:59</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>07:07</t>
+  </si>
+  <si>
+    <t>08:48</t>
+  </si>
+  <si>
+    <t>VN-A662</t>
+  </si>
+  <si>
     <t>13:02</t>
   </si>
   <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>13:46</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>08:38</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>15:57</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>11:58</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>13:29</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>07:34</t>
-  </si>
-  <si>
-    <t>09:29</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>16:06</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>08:09</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>10:56</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>10:21</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>10:34</t>
-  </si>
-  <si>
-    <t>12:43</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>11:03</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>07:59</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>10:44</t>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>VN-A666</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:01</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>06:49</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:43</t>
+  </si>
+  <si>
+    <t>13:09</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>09:26</t>
+  </si>
+  <si>
+    <t>11:18</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>12:49</t>
+  </si>
+  <si>
+    <t>16:17</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>15:11</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>10:22</t>
+  </si>
+  <si>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>09:13</t>
+  </si>
+  <si>
+    <t>11:27</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>10:52</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>10:08</t>
+  </si>
+  <si>
+    <t>12:17</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>14:14</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>11:33</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>09:23</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>12:04</t>
+  </si>
+  <si>
+    <t>13:49</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
+    <t>12:01</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>VN-A693</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>VN-A698</t>
+  </si>
+  <si>
+    <t>11:51</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A699</t>
+  </si>
+  <si>
+    <t>07:48</t>
   </si>
   <si>
     <t>12:39</t>
   </si>
   <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>09:43</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>12:37</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>09:01</t>
-  </si>
-  <si>
-    <t>12:09</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>07:23</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>10:47</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>886D</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:03</t>
-  </si>
-  <si>
-    <t>10:43</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>09:57</t>
-  </si>
-  <si>
-    <t>12:26</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>06:56</t>
-  </si>
-  <si>
-    <t>09:18</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>11:06</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>07:31</t>
-  </si>
-  <si>
-    <t>09:02</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>09:59</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>07:07</t>
-  </si>
-  <si>
-    <t>08:48</t>
-  </si>
-  <si>
-    <t>VN-A662</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A666</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:01</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>06:49</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:43</t>
-  </si>
-  <si>
-    <t>13:09</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>09:26</t>
-  </si>
-  <si>
-    <t>11:18</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>12:49</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>10:22</t>
-  </si>
-  <si>
-    <t>12:12</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>09:13</t>
-  </si>
-  <si>
-    <t>11:27</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>10:52</t>
-  </si>
-  <si>
-    <t>12:59</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>10:08</t>
-  </si>
-  <si>
-    <t>12:17</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>14:14</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>09:07</t>
-  </si>
-  <si>
-    <t>11:33</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>09:23</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
-    <t>12:04</t>
-  </si>
-  <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
-    <t>12:01</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>VN-A693</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>VN-A698</t>
-  </si>
-  <si>
-    <t>11:51</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A699</t>
-  </si>
-  <si>
-    <t>07:48</t>
-  </si>
-  <si>
     <t>01:15</t>
   </si>
   <si>
@@ -1460,9 +1511,6 @@
     <t>VN-A816</t>
   </si>
   <si>
-    <t>12:18</t>
-  </si>
-  <si>
     <t>VN-A817</t>
   </si>
   <si>
@@ -1481,7 +1529,7 @@
     <t>Total Record(s): 405</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 23, 2026 11:33</t>
+    <t xml:space="preserve">Generated on  Aug 23, 2026 12:23</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4456,7 +4504,9 @@
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
-      <c r="M86" s="7"/>
+      <c t="s" r="M86" s="7">
+        <v>180</v>
+      </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c t="s" r="A87" s="6">
@@ -4485,7 +4535,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4518,7 +4568,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4548,10 +4598,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4584,7 +4634,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4604,7 +4654,7 @@
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4619,7 +4669,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4631,17 +4681,17 @@
         <v>76</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="K92" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -4656,7 +4706,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4671,7 +4721,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="K93" s="7">
         <v>127</v>
@@ -4693,7 +4743,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4702,7 +4752,7 @@
         <v>51</v>
       </c>
       <c t="s" r="H94" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="I94" s="7">
         <v>120</v>
@@ -4726,13 +4776,13 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G95" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="H95" s="8">
         <v>51</v>
@@ -4741,7 +4791,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4759,7 +4809,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4771,10 +4821,10 @@
         <v>76</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4792,7 +4842,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4804,7 +4854,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J97" s="7">
         <v>147</v>
@@ -4840,7 +4890,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4852,7 +4902,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>74</v>
@@ -4860,7 +4910,7 @@
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -4875,7 +4925,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4884,13 +4934,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="I100" s="7">
         <v>57</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4908,22 +4958,22 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4941,7 +4991,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4950,7 +5000,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="I102" s="7">
         <v>147</v>
@@ -4989,7 +5039,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5009,7 +5059,7 @@
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5024,7 +5074,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5039,12 +5089,12 @@
         <v>125</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c t="s" r="M105" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
@@ -5059,7 +5109,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5077,11 +5127,11 @@
         <v>19</v>
       </c>
       <c t="s" r="K106" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L106" s="7"/>
       <c t="s" r="M106" s="7">
-        <v>138</v>
+        <v>209</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -5096,7 +5146,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5133,7 +5183,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5170,7 +5220,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5207,7 +5257,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5219,7 +5269,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>78</v>
@@ -5229,7 +5279,7 @@
       </c>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5244,7 +5294,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5256,17 +5306,17 @@
         <v>51</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="K111" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5296,7 +5346,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5305,18 +5355,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="I113" s="7">
         <v>148</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5331,27 +5381,27 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="H114" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5366,7 +5416,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5378,7 +5428,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J115" s="7">
         <v>179</v>
@@ -5386,7 +5436,7 @@
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5401,7 +5451,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5413,7 +5463,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>153</v>
@@ -5434,7 +5484,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5443,7 +5493,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I117" s="7">
         <v>22</v>
@@ -5467,13 +5517,13 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>16</v>
@@ -5500,7 +5550,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5509,13 +5559,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5533,22 +5583,22 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5581,7 +5631,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5593,7 +5643,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>63</v>
@@ -5601,7 +5651,7 @@
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -5616,7 +5666,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5649,7 +5699,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5658,13 +5708,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5682,22 +5732,22 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5730,7 +5780,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5748,11 +5798,11 @@
         <v>21</v>
       </c>
       <c t="s" r="K127" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>190</v>
+        <v>240</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -5767,7 +5817,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5785,11 +5835,11 @@
         <v>153</v>
       </c>
       <c t="s" r="K128" s="7">
-        <v>42</v>
+        <v>153</v>
       </c>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -5804,7 +5854,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5819,14 +5869,14 @@
         <v>94</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="K129" s="7">
-        <v>238</v>
+        <v>59</v>
       </c>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>145</v>
+        <v>234</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -5841,7 +5891,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5889,7 +5939,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5909,7 +5959,7 @@
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -5924,7 +5974,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5944,7 +5994,7 @@
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -5959,7 +6009,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5971,14 +6021,16 @@
         <v>151</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
-      <c r="M134" s="7"/>
+      <c t="s" r="M134" s="7">
+        <v>245</v>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c t="s" r="A135" s="6">
@@ -5992,7 +6044,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6004,7 +6056,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>108</v>
@@ -6025,7 +6077,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6040,7 +6092,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -6058,7 +6110,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6067,13 +6119,13 @@
         <v>151</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -6106,7 +6158,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6121,7 +6173,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6141,7 +6193,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6174,7 +6226,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6189,7 +6241,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6207,7 +6259,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6219,7 +6271,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>165</v>
@@ -6255,7 +6307,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6275,7 +6327,7 @@
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6290,7 +6342,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6302,7 +6354,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>78</v>
@@ -6323,7 +6375,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6335,7 +6387,7 @@
         <v>116</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>98</v>
@@ -6371,19 +6423,19 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>62</v>
@@ -6393,7 +6445,7 @@
       </c>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6408,7 +6460,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6423,7 +6475,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6441,7 +6493,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6453,10 +6505,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6474,7 +6526,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6483,10 +6535,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>47</v>
@@ -6507,13 +6559,13 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="H152" s="8">
         <v>16</v>
@@ -6522,7 +6574,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6555,13 +6607,13 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>51</v>
@@ -6570,12 +6622,12 @@
         <v>53</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>263</v>
+        <v>180</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6590,7 +6642,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6608,7 +6660,7 @@
         <v>66</v>
       </c>
       <c t="s" r="K155" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
@@ -6627,7 +6679,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6642,7 +6694,7 @@
         <v>172</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6675,7 +6727,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6687,15 +6739,15 @@
         <v>151</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6710,7 +6762,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6730,7 +6782,7 @@
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -6745,7 +6797,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6778,7 +6830,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6790,10 +6842,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6826,19 +6878,19 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>76</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>63</v>
@@ -6861,7 +6913,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6876,7 +6928,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6894,7 +6946,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6903,10 +6955,10 @@
         <v>51</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>168</v>
@@ -6942,7 +6994,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6975,7 +7027,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7023,13 +7075,13 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>51</v>
@@ -7038,7 +7090,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -7058,7 +7110,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7073,7 +7125,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c t="s" r="K171" s="7">
         <v>84</v>
@@ -7095,7 +7147,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7110,7 +7162,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7128,7 +7180,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7137,13 +7189,13 @@
         <v>51</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>121</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -7176,27 +7228,27 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7211,7 +7263,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7220,13 +7272,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="I176" s="7">
         <v>44</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7244,22 +7296,22 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7277,7 +7329,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7286,7 +7338,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c t="s" r="I178" s="7">
         <v>30</v>
@@ -7325,7 +7377,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7337,15 +7389,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7360,7 +7412,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7369,18 +7421,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7395,26 +7447,28 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>179</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
-      <c r="M182" s="7"/>
+      <c t="s" r="M182" s="7">
+        <v>294</v>
+      </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
       <c t="s" r="A183" s="6">
@@ -7428,7 +7482,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7437,13 +7491,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H183" s="8">
+        <v>226</v>
+      </c>
+      <c t="s" r="I183" s="7">
         <v>224</v>
       </c>
-      <c t="s" r="I183" s="7">
-        <v>222</v>
-      </c>
       <c t="s" r="J183" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7461,22 +7515,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>140</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7494,7 +7548,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7503,13 +7557,13 @@
         <v>140</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7527,22 +7581,22 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7575,19 +7629,19 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>157</v>
@@ -7595,7 +7649,7 @@
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7610,7 +7664,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7619,17 +7673,19 @@
         <v>34</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>40</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
-      <c r="M189" s="7"/>
+      <c t="s" r="M189" s="7">
+        <v>159</v>
+      </c>
     </row>
     <row r="190" ht="15" customHeight="1">
       <c t="s" r="A190" s="6">
@@ -7643,22 +7699,22 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7676,7 +7732,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7685,7 +7741,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c t="s" r="I191" s="7">
         <v>77</v>
@@ -7709,22 +7765,22 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7757,7 +7813,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7777,7 +7833,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -7792,7 +7848,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7804,15 +7860,15 @@
         <v>51</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -7827,7 +7883,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7860,7 +7916,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7893,7 +7949,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7908,7 +7964,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7926,7 +7982,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7938,10 +7994,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7974,7 +8030,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8007,7 +8063,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8022,7 +8078,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -8040,7 +8096,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8055,7 +8111,7 @@
         <v>146</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -8088,7 +8144,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8100,15 +8156,15 @@
         <v>151</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8123,7 +8179,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8135,14 +8191,16 @@
         <v>51</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>21</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
-      <c r="M206" s="7"/>
+      <c t="s" r="M206" s="7">
+        <v>317</v>
+      </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
       <c t="s" r="A207" s="6">
@@ -8156,7 +8214,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8168,10 +8226,10 @@
         <v>140</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8189,7 +8247,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8204,7 +8262,7 @@
         <v>108</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8222,7 +8280,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8231,10 +8289,10 @@
         <v>51</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>155</v>
@@ -8255,13 +8313,13 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>51</v>
@@ -8270,7 +8328,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8303,7 +8361,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8315,15 +8373,15 @@
         <v>51</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8338,7 +8396,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8350,10 +8408,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8373,7 +8431,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8388,11 +8446,13 @@
         <v>137</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
-      <c r="M214" s="7"/>
+      <c t="s" r="M214" s="7">
+        <v>326</v>
+      </c>
     </row>
     <row r="215" ht="15" customHeight="1">
       <c t="s" r="A215" s="6">
@@ -8406,7 +8466,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8439,7 +8499,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8472,7 +8532,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8484,10 +8544,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8516,17 +8576,17 @@
         <v>20</v>
       </c>
       <c t="s" r="C219" s="7">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>51</v>
@@ -8535,7 +8595,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8568,7 +8628,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8580,15 +8640,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -8603,7 +8663,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8623,7 +8683,7 @@
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8638,7 +8698,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8653,11 +8713,15 @@
         <v>138</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>190</v>
-      </c>
-      <c r="K223" s="7"/>
+        <v>191</v>
+      </c>
+      <c t="s" r="K223" s="7">
+        <v>63</v>
+      </c>
       <c r="L223" s="7"/>
-      <c r="M223" s="7"/>
+      <c t="s" r="M223" s="7">
+        <v>74</v>
+      </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
       <c t="s" r="A224" s="6">
@@ -8671,7 +8735,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8688,9 +8752,13 @@
       <c t="s" r="J224" s="7">
         <v>22</v>
       </c>
-      <c r="K224" s="7"/>
+      <c t="s" r="K224" s="7">
+        <v>141</v>
+      </c>
       <c r="L224" s="7"/>
-      <c r="M224" s="7"/>
+      <c t="s" r="M224" s="7">
+        <v>261</v>
+      </c>
     </row>
     <row r="225" ht="15" customHeight="1">
       <c t="s" r="A225" s="6">
@@ -8704,7 +8772,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8716,14 +8784,18 @@
         <v>34</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>25</v>
       </c>
-      <c r="K225" s="7"/>
+      <c t="s" r="K225" s="7">
+        <v>67</v>
+      </c>
       <c r="L225" s="7"/>
-      <c r="M225" s="7"/>
+      <c t="s" r="M225" s="7">
+        <v>334</v>
+      </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
       <c r="A226" s="6"/>
@@ -8752,7 +8824,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8761,10 +8833,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>131</v>
@@ -8772,7 +8844,7 @@
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -8787,19 +8859,19 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>103</v>
@@ -8807,7 +8879,7 @@
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>330</v>
+        <v>337</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -8822,7 +8894,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8831,18 +8903,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I229" s="7">
         <v>135</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -8857,13 +8929,13 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>16</v>
@@ -8890,7 +8962,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8899,10 +8971,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>154</v>
@@ -8923,13 +8995,13 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>16</v>
@@ -8938,7 +9010,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8956,7 +9028,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8968,10 +9040,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8989,7 +9061,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9001,10 +9073,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -9037,7 +9109,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9049,7 +9121,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>18</v>
@@ -9057,7 +9129,7 @@
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9072,7 +9144,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9081,18 +9153,18 @@
         <v>76</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9107,13 +9179,13 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>76</v>
@@ -9122,7 +9194,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -9140,7 +9212,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9149,13 +9221,13 @@
         <v>76</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -9188,7 +9260,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9203,7 +9275,7 @@
         <v>165</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -9223,7 +9295,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9235,15 +9307,15 @@
         <v>51</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9258,7 +9330,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9270,14 +9342,16 @@
         <v>133</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
-      <c r="M243" s="7"/>
+      <c t="s" r="M243" s="7">
+        <v>350</v>
+      </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
       <c t="s" r="A244" s="6">
@@ -9291,7 +9365,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9306,7 +9380,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9324,7 +9398,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9339,7 +9413,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9357,7 +9431,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9369,7 +9443,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>46</v>
@@ -9390,7 +9464,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9402,10 +9476,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9438,7 +9512,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9453,12 +9527,12 @@
         <v>35</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9473,7 +9547,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9488,12 +9562,12 @@
         <v>36</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -9508,7 +9582,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9520,7 +9594,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>93</v>
@@ -9545,7 +9619,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9560,7 +9634,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9578,7 +9652,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9590,10 +9664,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9626,7 +9700,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9635,7 +9709,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I255" s="7">
         <v>165</v>
@@ -9646,7 +9720,7 @@
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -9661,13 +9735,13 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>16</v>
@@ -9676,12 +9750,12 @@
         <v>98</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -9696,7 +9770,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9708,17 +9782,17 @@
         <v>34</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c t="s" r="K257" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>127</v>
+        <v>362</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9733,7 +9807,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9748,14 +9822,14 @@
         <v>127</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="K258" s="7">
-        <v>179</v>
+        <v>84</v>
       </c>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>66</v>
+        <v>120</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -9770,7 +9844,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9785,14 +9859,14 @@
         <v>66</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c t="s" r="K259" s="7">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>252</v>
+        <v>357</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -9807,7 +9881,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9825,11 +9899,11 @@
         <v>24</v>
       </c>
       <c t="s" r="K260" s="7">
-        <v>349</v>
+        <v>44</v>
       </c>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>200</v>
+        <v>25</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -9859,27 +9933,27 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>356</v>
+        <v>365</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -9894,7 +9968,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9916,7 +9990,7 @@
       </c>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>21</v>
+        <v>326</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -9931,7 +10005,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9946,7 +10020,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9964,7 +10038,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9997,7 +10071,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10030,7 +10104,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -10042,10 +10116,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -10078,7 +10152,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10093,12 +10167,12 @@
         <v>174</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10106,14 +10180,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B270" s="7">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c t="s" r="C270" s="7">
         <v>14</v>
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10128,10 +10202,10 @@
         <v>21</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c t="s" r="K270" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
@@ -10150,7 +10224,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10187,7 +10261,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10196,17 +10270,21 @@
         <v>16</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>30</v>
       </c>
-      <c r="K272" s="7"/>
+      <c t="s" r="K272" s="7">
+        <v>358</v>
+      </c>
       <c r="L272" s="7"/>
-      <c r="M272" s="7"/>
+      <c t="s" r="M272" s="7">
+        <v>113</v>
+      </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
       <c t="s" r="A273" s="6">
@@ -10220,26 +10298,30 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>362</v>
-      </c>
-      <c r="K273" s="7"/>
+        <v>371</v>
+      </c>
+      <c t="s" r="K273" s="7">
+        <v>372</v>
+      </c>
       <c r="L273" s="7"/>
-      <c r="M273" s="7"/>
+      <c t="s" r="M273" s="7">
+        <v>217</v>
+      </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
       <c r="A274" s="6"/>
@@ -10268,7 +10350,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10280,10 +10362,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -10303,7 +10385,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10315,14 +10397,16 @@
         <v>133</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
-      <c r="M276" s="7"/>
+      <c t="s" r="M276" s="7">
+        <v>245</v>
+      </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
       <c t="s" r="A277" s="6">
@@ -10336,7 +10420,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10369,7 +10453,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10402,7 +10486,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10417,7 +10501,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10435,7 +10519,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10444,13 +10528,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10468,22 +10552,22 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10516,7 +10600,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10528,7 +10612,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>35</v>
@@ -10536,7 +10620,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>369</v>
+        <v>379</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10551,7 +10635,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10571,7 +10655,7 @@
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10586,7 +10670,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10601,12 +10685,12 @@
         <v>125</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10621,7 +10705,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10656,7 +10740,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10668,7 +10752,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>74</v>
@@ -10689,7 +10773,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10701,10 +10785,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10722,7 +10806,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10737,7 +10821,7 @@
         <v>154</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10755,7 +10839,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10767,10 +10851,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>373</v>
+        <v>334</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10803,7 +10887,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10815,7 +10899,7 @@
         <v>151</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>126</v>
@@ -10823,7 +10907,7 @@
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>126</v>
+        <v>384</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -10838,7 +10922,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10847,7 +10931,7 @@
         <v>151</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I293" s="7">
         <v>138</v>
@@ -10871,13 +10955,13 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>151</v>
@@ -10904,7 +10988,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10919,7 +11003,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10952,7 +11036,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -10967,12 +11051,12 @@
         <v>98</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>376</v>
+        <v>386</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -10987,7 +11071,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -10999,15 +11083,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>377</v>
+        <v>387</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11022,7 +11106,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -11034,10 +11118,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -11055,7 +11139,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11067,10 +11151,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -11088,7 +11172,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11100,10 +11184,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11136,7 +11220,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11148,7 +11232,7 @@
         <v>151</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>157</v>
@@ -11171,7 +11255,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11183,15 +11267,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11206,7 +11290,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11218,7 +11302,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>87</v>
@@ -11239,7 +11323,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11251,10 +11335,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11287,7 +11371,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11296,10 +11380,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>100</v>
@@ -11307,7 +11391,7 @@
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>381</v>
+        <v>391</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11322,27 +11406,27 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>382</v>
+        <v>392</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11357,7 +11441,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11366,20 +11450,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c t="s" r="I310" s="7">
         <v>125</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="K310" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>384</v>
+        <v>394</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11394,13 +11478,13 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>16</v>
@@ -11412,11 +11496,11 @@
         <v>19</v>
       </c>
       <c t="s" r="K311" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>138</v>
+        <v>395</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11431,7 +11515,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11443,10 +11527,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11464,7 +11548,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11479,7 +11563,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11497,7 +11581,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11530,7 +11614,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11542,10 +11626,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11578,7 +11662,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11587,18 +11671,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c t="s" r="I317" s="7">
         <v>168</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11613,26 +11697,28 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>84</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
-      <c r="M318" s="7"/>
+      <c t="s" r="M318" s="7">
+        <v>399</v>
+      </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
       <c t="s" r="A319" s="6">
@@ -11646,7 +11732,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11655,7 +11741,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c t="s" r="I319" s="7">
         <v>87</v>
@@ -11679,13 +11765,13 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>16</v>
@@ -11712,7 +11798,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11724,10 +11810,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11760,7 +11846,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -11772,7 +11858,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>174</v>
@@ -11780,7 +11866,7 @@
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>392</v>
+        <v>404</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11795,7 +11881,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11810,12 +11896,12 @@
         <v>98</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>393</v>
+        <v>405</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -11830,7 +11916,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11842,10 +11928,10 @@
         <v>164</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11865,7 +11951,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -11877,7 +11963,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>84</v>
@@ -11898,7 +11984,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11913,7 +11999,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11931,7 +12017,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11943,7 +12029,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>44</v>
@@ -11964,7 +12050,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11976,7 +12062,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>121</v>
@@ -11997,7 +12083,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12012,7 +12098,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -12045,7 +12131,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -12057,7 +12143,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>100</v>
@@ -12080,7 +12166,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12095,12 +12181,12 @@
         <v>98</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>398</v>
+        <v>410</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12115,7 +12201,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -12127,15 +12213,15 @@
         <v>41</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12150,7 +12236,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12183,7 +12269,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12216,7 +12302,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12231,7 +12317,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -12249,7 +12335,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12261,10 +12347,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -12297,7 +12383,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -12309,7 +12395,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>167</v>
@@ -12317,7 +12403,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12332,7 +12418,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12347,12 +12433,12 @@
         <v>123</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>404</v>
+        <v>416</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12367,7 +12453,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -12376,18 +12462,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>103</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12402,26 +12488,28 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>104</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
-      <c r="M343" s="7"/>
+      <c t="s" r="M343" s="7">
+        <v>266</v>
+      </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
       <c t="s" r="A344" s="6">
@@ -12435,7 +12523,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -12447,7 +12535,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>143</v>
@@ -12468,7 +12556,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12480,7 +12568,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>25</v>
@@ -12516,7 +12604,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12525,13 +12613,13 @@
         <v>51</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12551,22 +12639,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12586,7 +12674,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12598,7 +12686,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>19</v>
@@ -12606,7 +12694,7 @@
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>221</v>
+        <v>418</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -12621,7 +12709,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12638,9 +12726,13 @@
       <c t="s" r="J350" s="7">
         <v>120</v>
       </c>
-      <c r="K350" s="7"/>
+      <c t="s" r="K350" s="7">
+        <v>64</v>
+      </c>
       <c r="L350" s="7"/>
-      <c r="M350" s="7"/>
+      <c t="s" r="M350" s="7">
+        <v>153</v>
+      </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
       <c t="s" r="A351" s="6">
@@ -12654,7 +12746,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12666,14 +12758,18 @@
         <v>164</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>43</v>
       </c>
-      <c r="K351" s="7"/>
+      <c t="s" r="K351" s="7">
+        <v>94</v>
+      </c>
       <c r="L351" s="7"/>
-      <c r="M351" s="7"/>
+      <c t="s" r="M351" s="7">
+        <v>59</v>
+      </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
       <c t="s" r="A352" s="6">
@@ -12687,7 +12783,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12704,9 +12800,13 @@
       <c t="s" r="J352" s="7">
         <v>96</v>
       </c>
-      <c r="K352" s="7"/>
+      <c t="s" r="K352" s="7">
+        <v>24</v>
+      </c>
       <c r="L352" s="7"/>
-      <c r="M352" s="7"/>
+      <c t="s" r="M352" s="7">
+        <v>193</v>
+      </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
       <c t="s" r="A353" s="6">
@@ -12720,7 +12820,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12732,14 +12832,18 @@
         <v>34</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>406</v>
-      </c>
-      <c r="K353" s="7"/>
+        <v>419</v>
+      </c>
+      <c t="s" r="K353" s="7">
+        <v>121</v>
+      </c>
       <c r="L353" s="7"/>
-      <c r="M353" s="7"/>
+      <c t="s" r="M353" s="7">
+        <v>203</v>
+      </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
       <c t="s" r="A354" s="6">
@@ -12753,7 +12857,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12768,11 +12872,15 @@
         <v>46</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>407</v>
-      </c>
-      <c r="K354" s="7"/>
+        <v>420</v>
+      </c>
+      <c t="s" r="K354" s="7">
+        <v>421</v>
+      </c>
       <c r="L354" s="7"/>
-      <c r="M354" s="7"/>
+      <c t="s" r="M354" s="7">
+        <v>172</v>
+      </c>
     </row>
     <row r="355" ht="15" customHeight="1">
       <c r="A355" s="6"/>
@@ -12801,7 +12909,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12816,12 +12924,12 @@
         <v>168</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>410</v>
+        <v>424</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -12836,7 +12944,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12848,7 +12956,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>137</v>
@@ -12856,7 +12964,7 @@
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -12871,7 +12979,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12883,10 +12991,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12904,7 +13012,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -12919,7 +13027,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12937,7 +13045,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -12946,13 +13054,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I360" s="7">
         <v>44</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12970,22 +13078,22 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -13018,7 +13126,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13030,15 +13138,15 @@
         <v>41</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>414</v>
+        <v>428</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13053,7 +13161,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13065,15 +13173,15 @@
         <v>23</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>416</v>
+        <v>430</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13088,7 +13196,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13100,15 +13208,15 @@
         <v>41</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13123,7 +13231,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -13143,7 +13251,7 @@
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>417</v>
+        <v>431</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13158,7 +13266,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13170,10 +13278,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -13191,7 +13299,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13206,7 +13314,7 @@
         <v>108</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -13224,7 +13332,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13236,7 +13344,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>27</v>
@@ -13257,7 +13365,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13269,10 +13377,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13305,7 +13413,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13314,7 +13422,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>82</v>
@@ -13325,7 +13433,7 @@
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>420</v>
+        <v>434</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13340,13 +13448,13 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>16</v>
@@ -13360,7 +13468,7 @@
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>421</v>
+        <v>435</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -13375,7 +13483,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -13390,11 +13498,13 @@
         <v>178</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
-      <c r="M374" s="7"/>
+      <c t="s" r="M374" s="7">
+        <v>73</v>
+      </c>
     </row>
     <row r="375" ht="15" customHeight="1">
       <c t="s" r="A375" s="6">
@@ -13408,7 +13518,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13420,7 +13530,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>94</v>
@@ -13441,7 +13551,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -13450,10 +13560,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>147</v>
@@ -13474,22 +13584,22 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13522,7 +13632,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13531,10 +13641,10 @@
         <v>51</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>19</v>
@@ -13542,7 +13652,7 @@
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>427</v>
+        <v>441</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -13557,13 +13667,13 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>51</v>
@@ -13572,11 +13682,13 @@
         <v>21</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
-      <c r="M380" s="7"/>
+      <c t="s" r="M380" s="7">
+        <v>442</v>
+      </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
       <c t="s" r="A381" s="6">
@@ -13590,7 +13702,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13599,7 +13711,7 @@
         <v>51</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c t="s" r="I381" s="7">
         <v>43</v>
@@ -13623,22 +13735,22 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13671,7 +13783,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13706,7 +13818,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13725,7 +13837,9 @@
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
-      <c r="M385" s="7"/>
+      <c t="s" r="M385" s="7">
+        <v>445</v>
+      </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
       <c t="s" r="A386" s="6">
@@ -13739,7 +13853,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13751,7 +13865,7 @@
         <v>133</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>154</v>
@@ -13772,7 +13886,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13784,10 +13898,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13805,7 +13919,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13814,10 +13928,10 @@
         <v>51</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>100</v>
@@ -13853,7 +13967,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -13865,15 +13979,15 @@
         <v>76</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -13888,7 +14002,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13900,15 +14014,15 @@
         <v>51</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>435</v>
+        <v>450</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -13923,7 +14037,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -13935,7 +14049,7 @@
         <v>164</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>178</v>
@@ -13943,7 +14057,7 @@
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>436</v>
+        <v>451</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -13958,7 +14072,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13970,7 +14084,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>21</v>
@@ -13991,7 +14105,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -14000,10 +14114,10 @@
         <v>51</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>153</v>
@@ -14024,19 +14138,19 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="H395" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>154</v>
@@ -14057,7 +14171,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -14072,7 +14186,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -14090,7 +14204,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -14102,7 +14216,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>47</v>
@@ -14138,7 +14252,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -14147,18 +14261,18 @@
         <v>51</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I399" s="7">
         <v>100</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>438</v>
+        <v>453</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14173,27 +14287,27 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>439</v>
+        <v>454</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14208,7 +14322,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -14241,7 +14355,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -14274,7 +14388,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
@@ -14286,10 +14400,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14322,7 +14436,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14337,12 +14451,12 @@
         <v>100</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>442</v>
+        <v>457</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14357,7 +14471,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14369,15 +14483,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>443</v>
+        <v>458</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14392,7 +14506,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14404,10 +14518,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14425,7 +14539,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14437,10 +14551,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14458,7 +14572,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -14470,10 +14584,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14506,7 +14620,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -14521,12 +14635,12 @@
         <v>168</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>446</v>
+        <v>461</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -14541,7 +14655,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -14553,15 +14667,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>447</v>
+        <v>462</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -14576,7 +14690,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -14585,13 +14699,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>118</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14609,22 +14723,22 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14642,7 +14756,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
@@ -14654,10 +14768,10 @@
         <v>133</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14675,7 +14789,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -14687,7 +14801,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>171</v>
@@ -14723,27 +14837,27 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="F418" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>450</v>
+        <v>465</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -14758,7 +14872,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="F419" s="7">
         <v>320</v>
@@ -14767,7 +14881,7 @@
         <v>51</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I419" s="7">
         <v>85</v>
@@ -14791,13 +14905,13 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="F420" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>51</v>
@@ -14806,7 +14920,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14824,7 +14938,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -14833,13 +14947,13 @@
         <v>51</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c t="s" r="I421" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14857,13 +14971,13 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>51</v>
@@ -14872,7 +14986,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14905,7 +15019,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -14925,7 +15039,7 @@
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>453</v>
+        <v>468</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -14940,7 +15054,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14955,12 +15069,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>454</v>
+        <v>469</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -14975,7 +15089,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -14987,7 +15101,7 @@
         <v>151</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J426" s="7">
         <v>72</v>
@@ -15008,7 +15122,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -15023,7 +15137,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -15041,7 +15155,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -15056,7 +15170,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -15074,7 +15188,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -15089,7 +15203,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -15107,7 +15221,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -15155,7 +15269,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -15164,18 +15278,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H432" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>456</v>
+        <v>471</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15190,22 +15304,22 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -15223,22 +15337,22 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I434" s="7">
         <v>142</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -15256,13 +15370,13 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>16</v>
@@ -15289,7 +15403,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -15304,7 +15418,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -15337,7 +15451,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -15349,15 +15463,15 @@
         <v>71</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
-        <v>458</v>
+        <v>473</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -15372,7 +15486,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -15384,14 +15498,16 @@
         <v>151</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
-      <c r="M439" s="7"/>
+      <c t="s" r="M439" s="7">
+        <v>474</v>
+      </c>
     </row>
     <row r="440" ht="15" customHeight="1">
       <c t="s" r="A440" s="6">
@@ -15405,7 +15521,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -15417,10 +15533,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -15438,7 +15554,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -15486,7 +15602,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="F443" s="7">
         <v>320</v>
@@ -15498,15 +15614,15 @@
         <v>140</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>460</v>
+        <v>476</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -15521,7 +15637,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="F444" s="7">
         <v>320</v>
@@ -15533,10 +15649,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15554,7 +15670,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="F445" s="7">
         <v>320</v>
@@ -15569,7 +15685,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -15587,7 +15703,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
@@ -15599,7 +15715,7 @@
         <v>151</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>109</v>
@@ -15620,7 +15736,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
@@ -15653,7 +15769,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
@@ -15668,7 +15784,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15701,7 +15817,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="F450" s="7">
         <v>321</v>
@@ -15713,7 +15829,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J450" s="7">
         <v>138</v>
@@ -15736,7 +15852,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="F451" s="7">
         <v>321</v>
@@ -15748,7 +15864,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="J451" s="7">
         <v>77</v>
@@ -15769,7 +15885,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="F452" s="7">
         <v>321</v>
@@ -15778,13 +15894,13 @@
         <v>51</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
@@ -15802,22 +15918,22 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="F453" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G453" s="8">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c t="s" r="H453" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -15850,7 +15966,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="F455" s="7">
         <v>321</v>
@@ -15862,7 +15978,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c t="s" r="J455" s="7">
         <v>117</v>
@@ -15870,7 +15986,7 @@
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>404</v>
+        <v>416</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -15885,7 +16001,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="F456" s="7">
         <v>321</v>
@@ -15900,12 +16016,12 @@
         <v>103</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
       <c t="s" r="M456" s="7">
-        <v>466</v>
+        <v>482</v>
       </c>
     </row>
     <row r="457" ht="14.25" customHeight="1">
@@ -15920,7 +16036,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="F457" s="7">
         <v>321</v>
@@ -15932,7 +16048,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c t="s" r="J457" s="7">
         <v>21</v>
@@ -15953,7 +16069,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="F458" s="7">
         <v>321</v>
@@ -15968,7 +16084,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -15986,7 +16102,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="F459" s="7">
         <v>321</v>
@@ -16019,7 +16135,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="F460" s="7">
         <v>321</v>
@@ -16034,7 +16150,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -16052,7 +16168,7 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="F461" s="7">
         <v>321</v>
@@ -16064,10 +16180,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -16100,7 +16216,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="F463" s="7">
         <v>320</v>
@@ -16112,15 +16228,15 @@
         <v>23</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
       <c t="s" r="M463" s="7">
-        <v>469</v>
+        <v>485</v>
       </c>
     </row>
     <row r="464" ht="14.25" customHeight="1">
@@ -16135,7 +16251,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="F464" s="7">
         <v>320</v>
@@ -16147,10 +16263,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -16170,7 +16286,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="F465" s="7">
         <v>320</v>
@@ -16182,15 +16298,15 @@
         <v>23</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c t="s" r="J465" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
       <c t="s" r="M465" s="7">
-        <v>327</v>
+        <v>486</v>
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1">
@@ -16205,7 +16321,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="F466" s="7">
         <v>320</v>
@@ -16217,7 +16333,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c t="s" r="J466" s="7">
         <v>158</v>
@@ -16238,7 +16354,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="F467" s="7">
         <v>320</v>
@@ -16247,13 +16363,13 @@
         <v>51</v>
       </c>
       <c t="s" r="H467" s="8">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="I467" s="7">
         <v>87</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
@@ -16271,13 +16387,13 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="F468" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G468" s="8">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="H468" s="8">
         <v>51</v>
@@ -16304,7 +16420,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="F469" s="7">
         <v>320</v>
@@ -16316,10 +16432,10 @@
         <v>160</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
@@ -16337,7 +16453,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="F470" s="7">
         <v>320</v>
@@ -16349,10 +16465,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -16385,7 +16501,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="F472" s="7">
         <v>330</v>
@@ -16397,15 +16513,15 @@
         <v>76</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
       <c t="s" r="M472" s="7">
-        <v>474</v>
+        <v>491</v>
       </c>
     </row>
     <row r="473" ht="14.25" customHeight="1">
@@ -16420,7 +16536,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="F473" s="7">
         <v>330</v>
@@ -16429,13 +16545,13 @@
         <v>76</v>
       </c>
       <c t="s" r="H473" s="8">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c t="s" r="I473" s="7">
         <v>63</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
@@ -16453,22 +16569,22 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="F474" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G474" s="8">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c t="s" r="H474" s="8">
         <v>76</v>
       </c>
       <c t="s" r="I474" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
@@ -16501,27 +16617,27 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="F476" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G476" s="8">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c t="s" r="H476" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I476" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J476" s="7">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="K476" s="7"/>
       <c r="L476" s="7"/>
       <c t="s" r="M476" s="7">
-        <v>238</v>
+        <v>261</v>
       </c>
     </row>
     <row r="477" ht="14.25" customHeight="1">
@@ -16536,7 +16652,7 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="F477" s="7">
         <v>330</v>
@@ -16545,13 +16661,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H477" s="8">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c t="s" r="I477" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J477" s="7">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="K477" s="7"/>
       <c r="L477" s="7"/>
@@ -16584,7 +16700,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="F479" s="7">
         <v>330</v>
@@ -16596,15 +16712,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I479" s="7">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
       <c t="s" r="M479" s="7">
-        <v>480</v>
+        <v>497</v>
       </c>
     </row>
     <row r="480" ht="15" customHeight="1">
@@ -16619,7 +16735,7 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="F480" s="7">
         <v>330</v>
@@ -16634,12 +16750,12 @@
         <v>176</v>
       </c>
       <c t="s" r="J480" s="7">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
       <c t="s" r="M480" s="7">
-        <v>337</v>
+        <v>126</v>
       </c>
     </row>
     <row r="481" ht="14.25" customHeight="1">
@@ -16654,7 +16770,7 @@
       </c>
       <c r="D481" s="7"/>
       <c t="s" r="E481" s="7">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="F481" s="7">
         <v>330</v>
@@ -16663,13 +16779,13 @@
         <v>76</v>
       </c>
       <c t="s" r="H481" s="8">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c t="s" r="I481" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J481" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K481" s="7"/>
       <c r="L481" s="7"/>
@@ -16687,13 +16803,13 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="F482" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G482" s="8">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c t="s" r="H482" s="8">
         <v>76</v>
@@ -16735,7 +16851,7 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="F484" s="7">
         <v>330</v>
@@ -16747,15 +16863,15 @@
         <v>76</v>
       </c>
       <c t="s" r="I484" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c t="s" r="J484" s="7">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
       <c t="s" r="M484" s="7">
-        <v>483</v>
+        <v>387</v>
       </c>
     </row>
     <row r="485" ht="15" customHeight="1">
@@ -16785,7 +16901,7 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="F486" s="7">
         <v>330</v>
@@ -16800,12 +16916,12 @@
         <v>103</v>
       </c>
       <c t="s" r="J486" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
       <c t="s" r="M486" s="7">
-        <v>485</v>
+        <v>501</v>
       </c>
     </row>
     <row r="487" ht="14.25" customHeight="1">
@@ -16820,7 +16936,7 @@
       </c>
       <c r="D487" s="7"/>
       <c t="s" r="E487" s="7">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="F487" s="7">
         <v>330</v>
@@ -16832,10 +16948,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I487" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J487" s="7">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="K487" s="7"/>
       <c r="L487" s="7"/>
@@ -16868,7 +16984,7 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="F489" s="7">
         <v>330</v>
@@ -16877,7 +16993,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H489" s="8">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c t="s" r="I489" s="7">
         <v>176</v>
@@ -16888,7 +17004,7 @@
       <c r="K489" s="7"/>
       <c r="L489" s="7"/>
       <c t="s" r="M489" s="7">
-        <v>488</v>
+        <v>504</v>
       </c>
     </row>
     <row r="490" ht="15" customHeight="1">
@@ -16903,22 +17019,22 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="F490" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G490" s="8">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c t="s" r="H490" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I490" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c t="s" r="J490" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K490" s="7"/>
       <c r="L490" s="7"/>
@@ -16926,7 +17042,7 @@
     </row>
     <row r="491" ht="15.75" customHeight="1">
       <c t="s" r="A491" s="9">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="B491" s="9"/>
       <c r="C491" s="9"/>
@@ -16946,7 +17062,7 @@
     <row r="492" ht="65.25" customHeight="1"/>
     <row r="493" ht="16.5" customHeight="1">
       <c t="s" r="A493" s="10">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="B493" s="10"/>
       <c r="C493" s="10"/>
@@ -16959,7 +17075,7 @@
       <c r="J493" s="10"/>
       <c r="K493" s="10"/>
       <c t="s" r="L493" s="11">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="M493" s="11"/>
       <c r="N493" s="11"/>
